--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104679_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104679_W25.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4359</v>
+        <v>3.5177</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1315</v>
+        <v>1.5844</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3044</v>
+        <v>1.9334</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.475</v>
+        <v>-1.4673</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6407</v>
+        <v>-0.6378</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8343</v>
+        <v>-0.8295</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.5216</v>
+        <v>-1.5417</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1354</v>
+        <v>-0.1486</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0466</v>
+        <v>0.0745</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7006</v>
+        <v>0.7768</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8287</v>
+        <v>0.3129</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8719</v>
+        <v>0.4639</v>
       </c>
       <c r="V2" t="n">
-        <v>2.6224</v>
+        <v>2.6147</v>
       </c>
       <c r="W2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7417</v>
+        <v>3.2287</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7959</v>
+        <v>1.6466</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9459</v>
+        <v>1.5821</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3387</v>
+        <v>0.34</v>
       </c>
       <c r="H3" t="n">
-        <v>0.528</v>
+        <v>0.5339</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5399</v>
+        <v>0.5089</v>
       </c>
       <c r="K3" t="n">
-        <v>0.436</v>
+        <v>0.4202</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1038</v>
+        <v>0.0887</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2011</v>
+        <v>-0.1689</v>
       </c>
       <c r="N3" t="n">
-        <v>0.092</v>
+        <v>0.1137</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0171</v>
+        <v>0.4936</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3902</v>
+        <v>0.2759</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6269</v>
+        <v>0.2178</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5504</v>
+        <v>2.7856</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5876</v>
+        <v>-0.0963</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9628</v>
+        <v>2.8819</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4785</v>
+        <v>2.4786</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9973</v>
+        <v>-0.9858</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4758</v>
+        <v>3.4643</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4528</v>
+        <v>2.4198</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4125</v>
+        <v>-0.4244</v>
       </c>
       <c r="L4" t="n">
-        <v>2.8653</v>
+        <v>2.8442</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0257</v>
+        <v>0.0588</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5848</v>
+        <v>-0.5613</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7029</v>
+        <v>-0.0604</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2359</v>
+        <v>-0.874</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9388</v>
+        <v>0.8135</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8227</v>
+        <v>0.8228</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.27</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0814</v>
+        <v>1.0695</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7181</v>
+        <v>2.3216</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6367</v>
+        <v>-1.2522</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0856</v>
+        <v>1.0755</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9119</v>
+        <v>1.91</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8264</v>
+        <v>-0.8345</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1376</v>
+        <v>1.1025</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6309</v>
+        <v>1.6095</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0521</v>
+        <v>-0.027</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2811</v>
+        <v>0.3005</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2725</v>
+        <v>-0.2823</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5293</v>
+        <v>0.1784</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8018</v>
+        <v>-0.4607</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. KNUDSEN</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5891</v>
+        <v>0.9469</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0492</v>
+        <v>0.7454</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6383</v>
+        <v>0.2015</v>
       </c>
       <c r="G6" t="n">
-        <v>1.297</v>
+        <v>2.6783</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3693</v>
+        <v>2.6796</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9276</v>
+        <v>-0.0013</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6646</v>
+        <v>2.7489</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0071</v>
+        <v>2.6372</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6717</v>
+        <v>0.1117</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6324</v>
+        <v>-0.0706</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3764</v>
+        <v>0.0424</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2559</v>
+        <v>-0.113</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6152</v>
+        <v>-0.1184</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4869</v>
+        <v>-0.272</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1282</v>
+        <v>0.1535</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5463</v>
+        <v>-0.7025</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5463</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>G. KNUDSEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4629</v>
+        <v>0.721</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4134</v>
+        <v>-0.0593</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0495</v>
+        <v>0.7803</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6743</v>
+        <v>1.3028</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6796</v>
+        <v>0.3732</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0053</v>
+        <v>0.9296</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7614</v>
+        <v>0.6563</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6495</v>
+        <v>-0.014</v>
       </c>
       <c r="L7" t="n">
-        <v>0.112</v>
+        <v>0.6703</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0871</v>
+        <v>0.6465</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0301</v>
+        <v>0.3871</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1172</v>
+        <v>0.2593</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.597</v>
+        <v>-0.4923</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6261</v>
+        <v>-0.4879</v>
       </c>
       <c r="U7" t="n">
-        <v>0.029</v>
+        <v>-0.0044</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7071</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8448</v>
+        <v>-0.5405</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2013</v>
+        <v>-0.969</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3566</v>
+        <v>0.4284</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1815</v>
+        <v>0.1863</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0131</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1946</v>
+        <v>0.1952</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0717</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4119</v>
+        <v>-0.1138</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1391</v>
+        <v>0.0975</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.569</v>
+        <v>-3.2824</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.8474</v>
+        <v>-3.8499</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2784</v>
+        <v>0.5676</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6079</v>
+        <v>-1.637</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4528</v>
+        <v>-2.4691</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8449</v>
+        <v>0.8321</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8117</v>
+        <v>-1.8693</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9475</v>
+        <v>-1.98</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1357</v>
+        <v>0.1106</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2038</v>
+        <v>0.2324</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7091</v>
+        <v>0.7215</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2577</v>
+        <v>0.5805</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1815</v>
+        <v>0.2549</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0762</v>
+        <v>0.3256</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2763</v>
+        <v>0.278</v>
       </c>
       <c r="W9" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3627</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0001</v>
+        <v>-3.6294</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3607</v>
+        <v>-3.1858</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6394</v>
+        <v>-0.4435</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.8261</v>
+        <v>-4.815</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2413</v>
+        <v>-0.2222</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.5848</v>
+        <v>-4.5928</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.6813</v>
+        <v>-3.6986</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.8198</v>
+        <v>-3.8365</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1447</v>
+        <v>-1.1164</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3798</v>
+        <v>-0.3601</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4915</v>
+        <v>0.8395</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3206</v>
+        <v>0.5128</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1709</v>
+        <v>0.3267</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.665</v>
+        <v>-4.6758</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.6544</v>
+        <v>-4.5773</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0106</v>
+        <v>-0.0985</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.5964</v>
+        <v>-4.6038</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4617</v>
+        <v>-1.4619</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.1347</v>
+        <v>-3.1419</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.7016</v>
+        <v>-4.7348</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9564</v>
+        <v>-0.9727</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.7452</v>
+        <v>-3.762</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1052</v>
+        <v>0.131</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3053</v>
+        <v>-0.2998</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6695</v>
+        <v>-0.5372</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3641</v>
+        <v>0.2374</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1441</v>
+        <v>1.1383</v>
       </c>
       <c r="W11" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.2946</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2175000000000002</v>
+        <v>0.1413000000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.4665</v>
+        <v>-6.4396</v>
       </c>
       <c r="F12" t="n">
-        <v>6.249199999999999</v>
+        <v>6.581</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.449800000000001</v>
+        <v>-4.4616</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3181</v>
+        <v>-0.2888999999999995</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.131900000000001</v>
+        <v>-4.172700000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.087899999999999</v>
+        <v>-4.3363</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4306</v>
+        <v>1.2996</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.5185</v>
+        <v>-5.636</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3617000000000001</v>
+        <v>-0.1251000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.7486</v>
+        <v>-1.5883</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3869</v>
+        <v>1.4631</v>
       </c>
       <c r="P12" t="n">
-        <v>2.268300000000001</v>
+        <v>2.2763</v>
       </c>
       <c r="Q12" t="n">
-        <v>-14.7442</v>
+        <v>-14.7961</v>
       </c>
       <c r="R12" t="n">
-        <v>17.0125</v>
+        <v>17.0724</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9678999999999998</v>
+        <v>1.3234</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9071999999999998</v>
+        <v>-0.5387</v>
       </c>
       <c r="U12" t="n">
-        <v>1.875</v>
+        <v>1.862</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9959999999999993</v>
+        <v>1.0032</v>
       </c>
       <c r="W12" t="n">
-        <v>13.2727</v>
+        <v>13.2314</v>
       </c>
       <c r="X12" t="n">
-        <v>-12.2766</v>
+        <v>-12.2282</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.919</v>
+        <v>5.3577</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4638</v>
+        <v>3.9188</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4552</v>
+        <v>1.4389</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5419</v>
+        <v>1.5164</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1692</v>
+        <v>0.1477</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3727</v>
+        <v>1.3688</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4078</v>
+        <v>-0.4676</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2851</v>
+        <v>-0.3252</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1228</v>
+        <v>-0.1424</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9497</v>
+        <v>1.984</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4542</v>
+        <v>0.4729</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4955</v>
+        <v>1.5112</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2184</v>
+        <v>-0.3181</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1815</v>
+        <v>-0.2886</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0369</v>
+        <v>-0.0295</v>
       </c>
       <c r="V13" t="n">
-        <v>2.571</v>
+        <v>2.5659</v>
       </c>
       <c r="W13" t="n">
-        <v>4.917</v>
+        <v>4.9026</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8285</v>
+        <v>4.5008</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6126</v>
+        <v>2.3042</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2159</v>
+        <v>2.1967</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1812</v>
+        <v>-1.2089</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3069</v>
+        <v>-0.3345</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8743</v>
+        <v>-0.8744</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.0969</v>
+        <v>-2.16</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2575</v>
+        <v>-0.3047</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.8393</v>
+        <v>-1.8553</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9157</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0494</v>
+        <v>-0.0298</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9651</v>
+        <v>0.9809</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4633</v>
+        <v>0.165</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3388</v>
+        <v>0.1063</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1246</v>
+        <v>0.0587</v>
       </c>
       <c r="V14" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W14" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6467000000000001</v>
+        <v>1.2131</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.3575</v>
+        <v>-1.0074</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0043</v>
+        <v>2.2205</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5431</v>
+        <v>-0.5244</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7591</v>
+        <v>-0.7528</v>
       </c>
       <c r="I15" t="n">
-        <v>0.216</v>
+        <v>0.2285</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6105</v>
+        <v>-0.6145</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0674</v>
+        <v>0.0901</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.398</v>
+        <v>0.144</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.747</v>
+        <v>-0.3929</v>
       </c>
       <c r="U15" t="n">
-        <v>0.349</v>
+        <v>0.5369</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4554</v>
+        <v>0.4809</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2315</v>
+        <v>-0.1701</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6869</v>
+        <v>0.651</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4494</v>
+        <v>1.1115</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.7957</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3541</v>
+        <v>0.3159</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.6714</v>
+        <v>0.8101</v>
       </c>
       <c r="K16" t="n">
-        <v>0.765</v>
+        <v>0.8101</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.4364</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.222</v>
+        <v>0.3014</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1397</v>
+        <v>-0.0144</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0823</v>
+        <v>0.3159</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6099</v>
+        <v>0.0523</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3206</v>
+        <v>0.1579</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2893</v>
+        <v>-0.1057</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4529</v>
+        <v>0.027</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.163</v>
+        <v>-1.1401</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6159</v>
+        <v>1.1671</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1125</v>
+        <v>1.7574</v>
       </c>
       <c r="H17" t="n">
-        <v>0.798</v>
+        <v>-0.0722</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3145</v>
+        <v>1.8296</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8139</v>
+        <v>0.6488</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8139</v>
+        <v>-0.6173</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.2661</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2986</v>
+        <v>1.1087</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0159</v>
+        <v>0.5451</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3145</v>
+        <v>0.5636</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0209</v>
+        <v>-0.4133</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1573</v>
+        <v>-0.4231</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1364</v>
+        <v>0.0097</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0042</v>
+        <v>-0.4236</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8929</v>
+        <v>-1.7435</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8887</v>
+        <v>1.3199</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7411</v>
+        <v>-0.4525</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0795</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8206</v>
+        <v>-1.3572</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6556</v>
+        <v>-1.7034</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6132</v>
+        <v>0.7477</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2688</v>
+        <v>-2.4511</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0856</v>
+        <v>1.2509</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5337</v>
+        <v>0.157</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5518999999999999</v>
+        <v>1.0939</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4258</v>
+        <v>0.733</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1875</v>
+        <v>-0.1492</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2383</v>
+        <v>0.8821</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.784</v>
+        <v>-0.5402</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0863</v>
+        <v>-0.5331</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8703</v>
+        <v>-0.0071</v>
       </c>
       <c r="G19" t="n">
-        <v>2.179</v>
+        <v>3.0592</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0332</v>
+        <v>1.562</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1458</v>
+        <v>1.4971</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1016</v>
+        <v>3.9307</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6896</v>
+        <v>2.5683</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7912</v>
+        <v>1.3624</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0773</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7228</v>
+        <v>-1.0062</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3546</v>
+        <v>0.1347</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-4.7803</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5093</v>
+        <v>-0.7085</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1603</v>
+        <v>-0.386</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6696</v>
+        <v>-0.3224</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-0.387</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0.7025</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.557</v>
+        <v>-0.7795</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1958</v>
+        <v>-0.0558</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3612</v>
+        <v>-0.7237</v>
       </c>
       <c r="G20" t="n">
-        <v>3.0508</v>
+        <v>2.1798</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5554</v>
+        <v>0.0317</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4954</v>
+        <v>2.1481</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9555</v>
+        <v>1.0872</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5802</v>
+        <v>-0.7002</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3753</v>
+        <v>1.7874</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9046999999999999</v>
+        <v>1.0926</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0248</v>
+        <v>0.7319</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1201</v>
+        <v>0.3608</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.7635</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2683</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.727</v>
+        <v>-0.504</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0948</v>
+        <v>0.0439</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6321</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3856</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="21">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7722</v>
+        <v>-1.8792</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.202</v>
+        <v>-2.4608</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4298</v>
+        <v>0.5815</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6901</v>
+        <v>-0.679</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1947</v>
+        <v>0.198</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8849</v>
+        <v>-0.877</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7056</v>
+        <v>0.6955</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4546</v>
+        <v>1.4479</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3957</v>
+        <v>-1.3745</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5039</v>
+        <v>0.3948</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1875</v>
+        <v>-0.4231</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6914</v>
+        <v>0.8179</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1122</v>
+        <v>-2.2769</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7197</v>
+        <v>-2.4969</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.411</v>
+        <v>-1.4045</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.707</v>
+        <v>-1.7088</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4861</v>
+        <v>-1.4931</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4861</v>
+        <v>-1.4931</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0751</v>
+        <v>0.0886</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2308</v>
+        <v>0.0593</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2601</v>
+        <v>-0.0234</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4908</v>
+        <v>0.0827</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8555</v>
+        <v>-5.473</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6493</v>
+        <v>-3.1963</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2062</v>
+        <v>-2.2767</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4849</v>
+        <v>-0.4826</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4158</v>
+        <v>-0.4109</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5976</v>
+        <v>-0.6085</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.303</v>
+        <v>-0.2851</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9548</v>
+        <v>-0.5794</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5565</v>
+        <v>-0.0838</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3983</v>
+        <v>-0.4956</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2173999999999987</v>
+        <v>0.2070999999999978</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.249000000000001</v>
+        <v>-6.581</v>
       </c>
       <c r="F24" t="n">
-        <v>6.466400000000001</v>
+        <v>6.788100000000002</v>
       </c>
       <c r="G24" t="n">
-        <v>4.449800000000001</v>
+        <v>4.4614</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3177999999999995</v>
+        <v>0.2889000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>4.131799999999999</v>
+        <v>4.172800000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3619000000000002</v>
+        <v>0.1251999999999998</v>
       </c>
       <c r="K24" t="n">
-        <v>1.7485</v>
+        <v>1.5885</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3866</v>
+        <v>-1.4633</v>
       </c>
       <c r="M24" t="n">
-        <v>4.088</v>
+        <v>4.336299999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4308</v>
+        <v>-1.2995</v>
       </c>
       <c r="O24" t="n">
-        <v>5.518599999999998</v>
+        <v>5.636200000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.2685</v>
+        <v>-2.2764</v>
       </c>
       <c r="Q24" t="n">
-        <v>-17.0126</v>
+        <v>-17.0724</v>
       </c>
       <c r="R24" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9677</v>
+        <v>-0.9748999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.8749</v>
+        <v>-1.862</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9073000000000001</v>
+        <v>0.8868999999999998</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9961999999999995</v>
+        <v>-1.003199999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>12.2767</v>
+        <v>12.2283</v>
       </c>
       <c r="X24" t="n">
-        <v>-13.2728</v>
+        <v>-13.2314</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104679_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104679_W25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-12.2282</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104679_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-13.2314</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
